--- a/artfynd/A 23817-2026 artfynd.xlsx
+++ b/artfynd/A 23817-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62617581</v>
+        <v>62704126</v>
       </c>
       <c r="B2" t="n">
-        <v>78595</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515039.7400881588</v>
+        <v>515040</v>
       </c>
       <c r="R2" t="n">
-        <v>6989816.259897427</v>
+        <v>6989816</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,24 +745,14 @@
           <t>2016-12-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-12-25</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På mossig sten</t>
+          <t>Riklig utbredning på stor sten nära sjön</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +779,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62704126</v>
+        <v>62617581</v>
       </c>
       <c r="B3" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +790,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>6461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515039.7400881588</v>
+        <v>515040</v>
       </c>
       <c r="R3" t="n">
-        <v>6989816.259897427</v>
+        <v>6989816</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,24 +849,14 @@
           <t>2016-12-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-12-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Riklig utbredning på stor sten nära sjön</t>
+          <t>På mossig sten</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 23817-2026 artfynd.xlsx
+++ b/artfynd/A 23817-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62704126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,8 +890,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62617581</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>